--- a/f_schedule/後台設定.xlsx
+++ b/f_schedule/後台設定.xlsx
@@ -866,8 +866,6 @@
           <t>R002</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>N</t>
@@ -883,8 +881,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -895,8 +891,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -914,21 +908,16 @@
           <t>R009</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -939,8 +928,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -958,21 +945,16 @@
           <t>R089</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -983,8 +965,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1002,7 +982,6 @@
           <t>R190</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>2F</t>
@@ -1013,14 +992,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1031,8 +1007,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1050,7 +1024,6 @@
           <t>R242</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>3F</t>
@@ -1061,14 +1034,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1079,8 +1049,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1098,8 +1066,6 @@
           <t>A000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>N</t>
@@ -1115,8 +1081,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1127,8 +1091,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1146,12 +1108,6 @@
           <t>A789</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>陳淑萍</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>N</t>
@@ -1167,8 +1123,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1179,10 +1133,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>陳詡善使用陳淑萍牌照</t>
+          <t>原名陳淑萍，已改名為陳詡善；舊文件上的陳淑萍即本人</t>
         </is>
       </c>
     </row>
@@ -1202,8 +1155,6 @@
           <t>A1011</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>N</t>
@@ -1219,8 +1170,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1231,8 +1180,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1250,21 +1197,16 @@
           <t>R081</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1275,8 +1217,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1294,21 +1234,16 @@
           <t>A456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1319,8 +1254,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,13 +1266,11 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>王淑環</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1350,13 +1281,11 @@
           <t>E5</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1367,7 +1296,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>洪瑞輝使用王淑環核章</t>
@@ -1385,22 +1313,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1411,8 +1333,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1425,9 +1345,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1438,13 +1355,11 @@
           <t>E3</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1455,8 +1370,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,9 +1382,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1482,13 +1392,11 @@
           <t>E1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1499,8 +1407,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1513,22 +1419,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1539,8 +1439,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1553,9 +1451,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1566,13 +1461,11 @@
           <t>E4</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1583,8 +1476,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1597,22 +1488,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1623,8 +1508,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1637,22 +1520,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1663,8 +1540,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1677,22 +1552,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1703,8 +1572,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1717,22 +1584,16 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1743,8 +1604,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1757,17 +1616,11 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1783,8 +1636,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1802,8 +1653,6 @@
           <t>a1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>N</t>
@@ -1814,9 +1663,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1832,7 +1678,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1850,8 +1695,6 @@
           <t>a2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>N</t>
@@ -1862,9 +1705,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1880,7 +1720,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1898,8 +1737,6 @@
           <t>a3</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>N</t>
@@ -1910,9 +1747,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1928,7 +1762,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1946,8 +1779,6 @@
           <t>a4</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>N</t>
@@ -1958,9 +1789,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1976,7 +1804,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1994,8 +1821,6 @@
           <t>a5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>N</t>
@@ -2006,9 +1831,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2024,7 +1846,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2037,9 +1858,6 @@
           <t>社工</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>N</t>
@@ -2050,13 +1868,6 @@
           <t>D*</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2069,9 +1880,6 @@
           <t>社工</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>N</t>
@@ -2082,13 +1890,6 @@
           <t>D.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2106,8 +1907,6 @@
           <t>2393</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2118,13 +1917,11 @@
           <t>D</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2135,7 +1932,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>特助,具照服資格可補台籍照服班</t>
@@ -2466,7 +2262,6 @@
           <t>特</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>特</t>
@@ -2489,7 +2284,6 @@
           <t>國</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>國</t>
@@ -2512,7 +2306,6 @@
           <t>R</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>(例/休)</t>
@@ -2535,7 +2328,6 @@
           <t>/</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>/</t>
@@ -3342,8 +3134,6 @@
           <t>王思宜</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>專門給王思宜使用的人頭</t>
@@ -3361,10 +3151,6 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3377,10 +3163,6 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3393,10 +3175,6 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3409,13 +3187,11 @@
           <t>護理</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>115.08.20</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>8/20 起才可使用</t>
@@ -3433,10 +3209,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3449,10 +3221,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3465,10 +3233,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3481,10 +3245,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3497,10 +3257,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3513,10 +3269,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3529,10 +3281,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3713,7 +3461,6 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3784,7 +3531,6 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3959,7 +3705,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>在此填入不要出現在F班的姓名</t>

--- a/f_schedule/後台設定.xlsx
+++ b/f_schedule/後台設定.xlsx
@@ -1266,11 +1266,6 @@
           <t>台籍照服</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>王淑環</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1298,7 +1293,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>洪瑞輝使用王淑環核章</t>
+          <t>核章人員欄原誤填王淑環，已更正：洪瑞輝即本人核章</t>
         </is>
       </c>
     </row>
